--- a/day4/result2.xlsx
+++ b/day4/result2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="190">
   <si>
     <t>无人机编号</t>
   </si>
@@ -497,6 +497,93 @@
   </si>
   <si>
     <t>并集总时长(s)</t>
+  </si>
+  <si>
+    <t>无人机编号</t>
+  </si>
+  <si>
+    <t>FY1</t>
+  </si>
+  <si>
+    <t>FY2</t>
+  </si>
+  <si>
+    <t>FY3</t>
+  </si>
+  <si>
+    <t>无人机运动方向</t>
+  </si>
+  <si>
+    <t>无人机运动速度(m/s)</t>
+  </si>
+  <si>
+    <t>投放点x(m)</t>
+  </si>
+  <si>
+    <t>投放点y(m)</t>
+  </si>
+  <si>
+    <t>投放点z(m)</t>
+  </si>
+  <si>
+    <t>起爆点x(m)</t>
+  </si>
+  <si>
+    <t>起爆点y(m)</t>
+  </si>
+  <si>
+    <t>起爆点z(m)</t>
+  </si>
+  <si>
+    <t>有效干扰时长(s)</t>
+  </si>
+  <si>
+    <t>注：以x轴为正向，逆时针方向为正，取值0~360（度）。云中心z&gt;=0（不许钻地）。</t>
+  </si>
+  <si>
+    <t>无人机</t>
+  </si>
+  <si>
+    <t>FY1</t>
+  </si>
+  <si>
+    <t>FY2</t>
+  </si>
+  <si>
+    <t>FY3</t>
+  </si>
+  <si>
+    <t>合计</t>
+  </si>
+  <si>
+    <t>内部θ(°)</t>
+  </si>
+  <si>
+    <t>t0(s)</t>
+  </si>
+  <si>
+    <t>tau(s)</t>
+  </si>
+  <si>
+    <t>起爆时刻(s)</t>
+  </si>
+  <si>
+    <t>爆点z(m)</t>
+  </si>
+  <si>
+    <t>窗口</t>
+  </si>
+  <si>
+    <t>[2.505,7.242]</t>
+  </si>
+  <si>
+    <t>[10.182,15.142]</t>
+  </si>
+  <si>
+    <t>[58.474,64.656]</t>
+  </si>
+  <si>
+    <t>时长(s)</t>
   </si>
 </sst>
 </file>
@@ -517,7 +604,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -543,11 +630,14 @@
     <border/>
     <border/>
     <border/>
+    <border/>
+    <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
@@ -567,6 +657,9 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -579,11 +672,11 @@
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="51.07421875" customWidth="true"/>
+    <col min="1" max="1" width="74.89453125" customWidth="true"/>
     <col min="2" max="2" width="15.16796875" customWidth="true"/>
     <col min="3" max="3" width="19.7109375" customWidth="true"/>
     <col min="4" max="4" width="11.7109375" customWidth="true"/>
-    <col min="5" max="5" width="11.7109375" customWidth="true"/>
+    <col min="5" max="5" width="10.984375" customWidth="true"/>
     <col min="6" max="6" width="10.89453125" customWidth="true"/>
     <col min="7" max="7" width="11.7109375" customWidth="true"/>
     <col min="8" max="8" width="11.7109375" customWidth="true"/>
@@ -593,45 +686,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="B2" s="0">
-        <v>178.86019999999999</v>
+        <v>176.92599999999999</v>
       </c>
       <c r="C2" s="0">
-        <v>139.81</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="D2" s="0">
         <v>17800</v>
@@ -643,85 +736,85 @@
         <v>1800</v>
       </c>
       <c r="G2" s="0">
-        <v>17300.040516774276</v>
+        <v>17618.898960384904</v>
       </c>
       <c r="H2" s="0">
-        <v>9.9471375972919134</v>
+        <v>9.7256616398043132</v>
       </c>
       <c r="I2" s="0">
-        <v>1737.3153638389999</v>
+        <v>1769.2523775</v>
       </c>
       <c r="J2" s="0">
-        <v>16.359747700842874</v>
+        <v>4.7372840829811205</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="B3" s="0">
-        <v>281.15359999999998</v>
+        <v>281.16159999999996</v>
       </c>
       <c r="C3" s="0">
-        <v>135.33000000000001</v>
+        <v>135.33800000000002</v>
       </c>
       <c r="D3" s="0">
-        <v>12114.707718643414</v>
+        <v>12114.795736272179</v>
       </c>
       <c r="E3" s="0">
-        <v>818.21130443368418</v>
+        <v>818.1929349737544</v>
       </c>
       <c r="F3" s="0">
         <v>1400</v>
       </c>
       <c r="G3" s="0">
-        <v>12266.475941482247</v>
+        <v>12266.680414038841</v>
       </c>
       <c r="H3" s="0">
-        <v>48.454591999133072</v>
+        <v>48.411918156542583</v>
       </c>
       <c r="I3" s="0">
         <v>1235.3060693749999</v>
       </c>
       <c r="J3" s="0">
-        <v>16.359747700842874</v>
+        <v>4.9596161266943231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="B4" s="0">
-        <v>151.9264</v>
+        <v>151.81440000000001</v>
       </c>
       <c r="C4" s="0">
-        <v>136.04300000000001</v>
+        <v>135.50700000000015</v>
       </c>
       <c r="D4" s="0">
-        <v>1388.2501020841946</v>
+        <v>1419.8176799396124</v>
       </c>
       <c r="E4" s="0">
-        <v>-540.28497887544563</v>
+        <v>-545.60966809556157</v>
       </c>
       <c r="F4" s="0">
         <v>700</v>
       </c>
       <c r="G4" s="0">
-        <v>1.1420372903874068</v>
+        <v>38.089036100546082</v>
       </c>
       <c r="H4" s="0">
-        <v>199.54060109329464</v>
+        <v>194.81968335202941</v>
       </c>
       <c r="I4" s="0">
-        <v>45.682407798999975</v>
+        <v>44.232057974999861</v>
       </c>
       <c r="J4" s="0">
-        <v>16.359747700842874</v>
+        <v>6.1815773318636147</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -730,70 +823,77 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.16796875" customWidth="true"/>
     <col min="2" max="2" width="9.34765625" customWidth="true"/>
-    <col min="3" max="3" width="6.7109375" customWidth="true"/>
-    <col min="4" max="4" width="6.7109375" customWidth="true"/>
+    <col min="3" max="3" width="7.7109375" customWidth="true"/>
+    <col min="4" max="4" width="7.7109375" customWidth="true"/>
     <col min="5" max="5" width="11.2578125" customWidth="true"/>
-    <col min="6" max="6" width="13.984375" customWidth="true"/>
-    <col min="7" max="7" width="13.2578125" customWidth="true"/>
+    <col min="6" max="6" width="11.7109375" customWidth="true"/>
+    <col min="7" max="7" width="13.984375" customWidth="true"/>
+    <col min="8" max="8" width="11.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>160</v>
+        <v>185</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="B2" s="0">
-        <v>1.1397999999999999</v>
+        <v>3.0739999999999998</v>
       </c>
       <c r="C2" s="0">
         <v>0</v>
       </c>
       <c r="D2" s="0">
-        <v>3.5767000000000002</v>
+        <v>2.5049999999999999</v>
       </c>
       <c r="E2" s="0">
-        <v>3.5767000000000002</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="G2" s="0">
-        <v>16.359747700842874</v>
+        <v>2.5049999999999999</v>
+      </c>
+      <c r="F2" s="0">
+        <v>1769.2523775</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="H2" s="0">
+        <v>4.7372840829811205</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="B3" s="0">
-        <v>-101.1536</v>
+        <v>-101.16159999999999</v>
       </c>
       <c r="C3" s="0">
         <v>4.3818000000000001</v>
@@ -804,34 +904,54 @@
       <c r="E3" s="0">
         <v>10.179300000000001</v>
       </c>
-      <c r="F3" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="G3" s="0">
-        <v>16.359747700842874</v>
+      <c r="F3" s="0">
+        <v>1235.3060693749999</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="H3" s="0">
+        <v>4.9596161266943231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="B4" s="0">
-        <v>28.073599999999999</v>
+        <v>28.185599999999994</v>
       </c>
       <c r="C4" s="0">
-        <v>38.419499999999999</v>
+        <v>38.347500000000004</v>
       </c>
       <c r="D4" s="0">
-        <v>11.5557</v>
+        <v>11.5685</v>
       </c>
       <c r="E4" s="0">
-        <v>49.975200000000001</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="G4" s="0">
-        <v>16.359747700842874</v>
+        <v>49.916000000000004</v>
+      </c>
+      <c r="F4" s="0">
+        <v>44.232057974999861</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="H4" s="0">
+        <v>6.1815773318636147</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" s="0"/>
+      <c r="C5" s="0"/>
+      <c r="D5" s="0"/>
+      <c r="E5" s="0"/>
+      <c r="F5" s="0"/>
+      <c r="G5" s="0"/>
+      <c r="H5" s="0">
+        <v>15.878477541539059</v>
       </c>
     </row>
   </sheetData>
